--- a/jpcore-r4b/develop/StructureDefinition-jp-organization-department.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-organization-department.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-organization-department.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-organization-department.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="366">
   <si>
     <t>Property</t>
   </si>
@@ -271,8 +271,8 @@
     <t>診療科は医療機関（Organization）の一部として、partOf要素を使用して親組織を参照することが推奨される。診療科の種別はtype要素でdept（部門）を指定する。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}org-1:組織は少なくとも名前またはidentifierを持つ必要があり、おそらく1つ以上のものもあるかもしれません / The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -297,13 +297,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -316,16 +316,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -336,13 +336,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -355,19 +355,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -387,13 +387,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト要約 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -413,19 +413,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -443,33 +443,33 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -498,7 +498,7 @@
    - SS-MIX2で定義された診療科コードを使用</t>
   </si>
   <si>
-    <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
+    <t>組織は様々なIDで知られている。一部の機関は複数のIDを維持し、ほとんどの機関は組織に関する他の組織との交換のために識別子を収集する。 / Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -512,7 +512,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 jp-org-dept-identifier-local-system:ローカル診療科コードのsystemは 'http://jpfhir.jp/fhir/core/mhlw/CodeSystem/MedicationRequestDepartment/[1+施設番号10桁]'でなければならない。 {system.all(substring(0,43)!='http://jpfhir.jp/fhir/core/mhlw/CodeSystem/MedicationRequestDepartment/' or substring(43).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
   </si>
   <si>
@@ -549,10 +549,10 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -567,7 +567,13 @@
     <t>Organization.identifier.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -580,22 +586,26 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Organization.identifier:ssmixDepartmentCode.use</t>
   </si>
   <si>
     <t>Organization.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
@@ -605,6 +615,10 @@
   </si>
   <si>
     <t>Identifier.use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Role.code or implied by context</t>
@@ -620,16 +634,16 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -656,10 +670,10 @@
     <t>SS-MIX2で定義された診療科コード体系を示すURI。</t>
   </si>
   <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jami.jp/SS-MIX2/CodeSystem/ClinicalDepartment</t>
@@ -724,10 +738,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -752,13 +766,13 @@
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -780,20 +794,21 @@
 </t>
   </si>
   <si>
-    <t>Whether the organization's record is still in active use</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use.</t>
-  </si>
-  <si>
-    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
+    <t>その組織の記録がまだ活発に使用されているかどうか / Whether the organization's record is still in active use</t>
+  </si>
+  <si>
+    <t>その組織の記録がまだ活用されているかどうか。 / Whether the organization's record is still in active use.</t>
+  </si>
+  <si>
+    <t>このアクティブなフラグは、組織を一時的に閉鎖したり、建設中のマークとして使用するために意図されていません。代わりに、組織内の場所に中断ステータスを設定する必要があります。中断の理由の詳細が必要な場合は、この要素の拡張機能を使用する必要があります。
+この要素は修飾子としてラベル付けされています。これは、リソースが誤って作成されたことを示すために使用できるためです。 / This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
 This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
   </si>
   <si>
-    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+    <t>レコードが使用されなくなり、UIでユーザーに対して一般的に非表示にされるべきであることを示すフラグが必要。 / Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
+  </si>
+  <si>
+    <t>active要素に値が提供されない場合、このリソースは一般的にアクティブであると見なされる / This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
     <t>No equivalent in HL7 v2</t>
@@ -811,24 +826,26 @@
     <t>Organization.type</t>
   </si>
   <si>
-    <t>Kind of organization</t>
-  </si>
-  <si>
-    <t>The kind(s) of organization that this is.</t>
-  </si>
-  <si>
-    <t>Organizations can be corporations, wards, sections, clinical teams, government departments, etc. Note that code is generally a classifier of the type of organization; in many applications, codes are used to identity a particular organization (say, ward) as opposed to another of the same type - these are identifiers, not codes
+    <t>組織の種類 / Kind of organization</t>
+  </si>
+  <si>
+    <t>これがどのような組織であるか。 / The kind(s) of organization that this is.</t>
+  </si>
+  <si>
+    <t>組織には、法人、区、部門、クリニカルチーム、政府省庁などがあります。 コードは一般的に組織のタイプの分類子であることに注意してください。 多くのアプリケーションでは、コードが特定の組織（例えば、区）を識別するために使用されます。同じタイプの他の組織と区別するためのidentifierであることに注意してください。
+複数のタイプが適切かどうかを考慮するときは、子組織を概念のより適切な使用として評価する必要があります。異なるタイプはおそらく組織の異なるサブエリアにあります。これは、宗教的、学術的、医療センターなど、直交的な値を持つタイプ値がある場合に最もよく使用されます。
+このオプションをシングルカーディナリティにプロファイルするものがいくつかの管轄権に存在することを期待しています。 / Organizations can be corporations, wards, sections, clinical teams, government departments, etc. Note that code is generally a classifier of the type of organization; in many applications, codes are used to identity a particular organization (say, ward) as opposed to another of the same type - these are identifiers, not codes
 When considering if multiple types are appropriate, you should evaluate if child organizations would be a more appropriate use of the concept, as different types likely are in different sub-areas of the organization. This is most likely to be used where type values have orthogonal values, such as a religious, academic and medical center.
 We expect that some jurisdictions will profile this optionality to be a single cardinality.</t>
   </si>
   <si>
-    <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
+    <t>これがどの種類の組織であるかを追跡できる必要がある - 異なる組織タイプには異なる用途がある。 / Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Used to categorize the organization.</t>
+    <t>組織を分類するために使用されます。 / Used to categorize the organization.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type|4.3.0</t>
@@ -873,16 +890,16 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>Name used for the organization</t>
-  </si>
-  <si>
-    <t>A name associated with the organization.</t>
-  </si>
-  <si>
-    <t>If the name of an organization changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
-  </si>
-  <si>
-    <t>Need to use the name as the label of the organization.</t>
+    <t>組織で使用される名前 / Name used for the organization</t>
+  </si>
+  <si>
+    <t>組織に関連する名前。 / A name associated with the organization.</t>
+  </si>
+  <si>
+    <t>もし団体の名前が変更された場合、検索によってまだ見つけられるように、旧名をエイリアス欄に入れることを検討してください。 / If the name of an organization changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
+  </si>
+  <si>
+    <t>組織のラベルとして名前を使用する必要がある。 / Need to use the name as the label of the organization.</t>
   </si>
   <si>
     <t>XON.1</t>
@@ -897,16 +914,17 @@
     <t>Organization.alias</t>
   </si>
   <si>
-    <t>A list of alternate names that the organization is known as, or was known as in the past</t>
-  </si>
-  <si>
-    <t>A list of alternate names that the organization is known as, or was known as in the past.</t>
-  </si>
-  <si>
-    <t>There are no dates associated with the alias/historic names, as this is not intended to track when names were used, but to assist in searching so that older names can still result in identifying the organization.</t>
-  </si>
-  <si>
-    <t>Over time locations and organizations go through many changes and can be known by different names.
+    <t>組織が以前に知られていた、または今でも知られている代替名のリスト。 / A list of alternate names that the organization is known as, or was known as in the past</t>
+  </si>
+  <si>
+    <t>その団体が過去に知られていた、または今でも知られている別名のリスト。 / A list of alternate names that the organization is known as, or was known as in the past.</t>
+  </si>
+  <si>
+    <t>エイリアス/履歴上の名前に関連付けられた日付はありません。これは、名前がいつ使用されたかを追跡するためではなく、古い名前でも組織を特定できるように検索を支援するためのものです。 / There are no dates associated with the alias/historic names, as this is not intended to track when names were used, but to assist in searching so that older names can still result in identifying the organization.</t>
+  </si>
+  <si>
+    <t>時間の経過とともにロケーションと組織は多くの変更を経て、異なる名前で知られるようになる。
+検索時に組織が以前知られていた名前を知ることは非常に有用である。 / Over time locations and organizations go through many changes and can be known by different names.
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
@@ -917,24 +935,24 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
-  </si>
-  <si>
-    <t>A contact detail for the organization.</t>
-  </si>
-  <si>
-    <t>The use code 'home' is not to be used. Note that these contacts are not the contact details of people who are employed by or represent the organization, but official contacts for the organization itself.</t>
-  </si>
-  <si>
-    <t>Human contact for the organization.</t>
+    <t>組織の連絡先詳細 / A contact detail for the organization</t>
+  </si>
+  <si>
+    <t>組織の連絡先詳細。 / A contact detail for the organization.</t>
+  </si>
+  <si>
+    <t>‘home’という利用コードは使用しないでください。これらの連絡先は、組織に雇用または代表されている人々の連絡先ではなく、組織自体の公式連絡先であることに注意してください。 / The use code 'home' is not to be used. Note that these contacts are not the contact details of people who are employed by or represent the organization, but official contacts for the organization itself.</t>
+  </si>
+  <si>
+    <t>組織への人的連絡先。 / Human contact for the organization.</t>
   </si>
   <si>
     <t xml:space="preserve">org-3
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+org-3:組織のテレコムは、家庭で使用することはできません。 / The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
     <t>ORC-22?</t>
@@ -953,24 +971,24 @@
 </t>
   </si>
   <si>
-    <t>An address for the organization</t>
-  </si>
-  <si>
-    <t>An address for the organization.</t>
-  </si>
-  <si>
-    <t>Organization may have multiple addresses with different uses or applicable periods. The use code 'home' is not to be used.</t>
-  </si>
-  <si>
-    <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
+    <t>組織の住所 / An address for the organization</t>
+  </si>
+  <si>
+    <t>組織の住所。 / An address for the organization.</t>
+  </si>
+  <si>
+    <t>組織は複数の住所を持つ場合があり、異なる用途や有効期間があります。使用コード 'home' は使用しないでください。 / Organization may have multiple addresses with different uses or applicable periods. The use code 'home' is not to be used.</t>
+  </si>
+  <si>
+    <t>連絡、請求、または報告要件のために組織の住所を追跡する必要がある場合がある。 / May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
   </si>
   <si>
     <t xml:space="preserve">org-2
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+org-2:組織の住所は「家」として使用することはできません。 / An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
     <t>ORC-23?</t>
@@ -998,7 +1016,7 @@
     <t>診療科は通常、医療機関に所属するため、partOf要素で親組織を参照することが推奨される。</t>
   </si>
   <si>
-    <t>Need to be able to track the hierarchy of organizations within an organization.</t>
+    <t>組織内の組織の階層を追跡できる必要がある。 / Need to be able to track the hierarchy of organizations within an organization.</t>
   </si>
   <si>
     <t>.playedBy[classCode=Part].scoper</t>
@@ -1011,19 +1029,19 @@
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
-  </si>
-  <si>
-    <t>Contact for the organization for a certain purpose.</t>
-  </si>
-  <si>
-    <t>Where multiple contacts for the same purpose are provided there is a standard extension that can be used to determine which one is the preferred contact to use.</t>
-  </si>
-  <si>
-    <t>Need to keep track of assigned contact points within bigger organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>特定の目的のための組織への連絡 / Contact for the organization for a certain purpose</t>
+  </si>
+  <si>
+    <t>特定の目的のための組織への連絡。 / Contact for the organization for a certain purpose.</t>
+  </si>
+  <si>
+    <t>同じ目的の複数の連絡先が提供される場合、優先的に使用する連絡先を特定するために使用できる標準拡張があります。 / Where multiple contacts for the same purpose are provided there is a standard extension that can be used to determine which one is the preferred contact to use.</t>
+  </si>
+  <si>
+    <t>大きな組織内で割り当てられた連絡先を追跡する必要がある。 / Need to keep track of assigned contact points within bigger organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1033,7 +1051,16 @@
     <t>Organization.contact.id</t>
   </si>
   <si>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>Organization.contact.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Organization.contact.modifierExtension</t>
@@ -1043,10 +1070,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1056,16 +1084,16 @@
     <t>Organization.contact.purpose</t>
   </si>
   <si>
-    <t>The type of contact</t>
-  </si>
-  <si>
-    <t>Indicates a purpose for which the contact can be reached.</t>
-  </si>
-  <si>
-    <t>Need to distinguish between multiple contact persons.</t>
-  </si>
-  <si>
-    <t>The purpose for which you would contact a contact party.</t>
+    <t>接触の種類 / The type of contact</t>
+  </si>
+  <si>
+    <t>連絡先に到達できる目的を示しています。 / Indicates a purpose for which the contact can be reached.</t>
+  </si>
+  <si>
+    <t>複数の連絡担当者を区別する必要がある。 / Need to distinguish between multiple contact persons.</t>
+  </si>
+  <si>
+    <t>「連絡を取りたい目的のための連絡先」となります。 / The purpose for which you would contact a contact party.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.3.0</t>
@@ -1081,13 +1109,13 @@
 </t>
   </si>
   <si>
-    <t>A name associated with the contact</t>
-  </si>
-  <si>
-    <t>A name associated with the contact.</t>
-  </si>
-  <si>
-    <t>Need to be able to track the person by name.</t>
+    <t>コンタクトに関連する名前 / A name associated with the contact</t>
+  </si>
+  <si>
+    <t>連絡関係にある名前 / A name associated with the contact.</t>
+  </si>
+  <si>
+    <t>名前で人を追跡できる必要がある。 / Need to be able to track the person by name.</t>
   </si>
   <si>
     <t>PID-5, PID-9</t>
@@ -1099,13 +1127,13 @@
     <t>Organization.contact.telecom</t>
   </si>
   <si>
-    <t>Contact details (telephone, email, etc.)  for a contact</t>
-  </si>
-  <si>
-    <t>A contact detail (e.g. a telephone number or an email address) by which the party may be contacted.</t>
-  </si>
-  <si>
-    <t>People have (primary) ways to contact them in some way such as phone, email.</t>
+    <t>連絡先詳細（電話、メールなど）連絡先のため / Contact details (telephone, email, etc.)  for a contact</t>
+  </si>
+  <si>
+    <t>当該のパーティーと連絡を取るための連絡先情報（例：電話番号やメールアドレス） / A contact detail (e.g. a telephone number or an email address) by which the party may be contacted.</t>
+  </si>
+  <si>
+    <t>人には電話やメールなど（主な）連絡方法がある。 / People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
     <t>PID-13, PID-14</t>
@@ -1117,13 +1145,13 @@
     <t>Organization.contact.address</t>
   </si>
   <si>
-    <t>Visiting or postal addresses for the contact</t>
-  </si>
-  <si>
-    <t>Visiting or postal addresses for the contact.</t>
-  </si>
-  <si>
-    <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
+    <t>連絡のための訪問先または郵送先の住所 / Visiting or postal addresses for the contact</t>
+  </si>
+  <si>
+    <t>連絡先の訪問または郵便送付先 / Visiting or postal addresses for the contact.</t>
+  </si>
+  <si>
+    <t>連絡先の住所を連絡、請求、または報告要件のために追跡する必要がある場合がある。 / May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
   </si>
   <si>
     <t>PID-11</t>
@@ -1139,13 +1167,13 @@
 </t>
   </si>
   <si>
-    <t>Technical endpoints providing access to services operated for the organization</t>
-  </si>
-  <si>
-    <t>Technical endpoints providing access to services operated for the organization.</t>
-  </si>
-  <si>
-    <t>Organizations have multiple systems that provide various services and need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
+    <t>「組織が運営するサービスへのアクセスを提供する技術エンドポイント」という意味です。 / Technical endpoints providing access to services operated for the organization</t>
+  </si>
+  <si>
+    <t>組織が運営するサービスへのアクセスを提供する技術的なエンドポイント。 / Technical endpoints providing access to services operated for the organization.</t>
+  </si>
+  <si>
+    <t>組織は様々なサービスを提供する複数のシステムを持ち、それらへの接続方法と目的の技術的な接続詳細を定義できる必要がある。 / Organizations have multiple systems that provide various services and need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1504,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="46.38671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="70.55078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="41.5390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3016,13 +3044,13 @@
         <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3060,10 +3088,10 @@
         <v>78</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>78</v>
@@ -3072,7 +3100,7 @@
         <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3084,7 +3112,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -3101,10 +3129,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3130,16 +3158,16 @@
         <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3164,11 +3192,11 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3186,7 +3214,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3198,13 +3226,13 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>134</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3215,10 +3243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3241,19 +3269,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3278,11 +3306,11 @@
         <v>78</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>78</v>
@@ -3300,7 +3328,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3312,13 +3340,13 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3329,10 +3357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3358,29 +3386,29 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>78</v>
@@ -3416,7 +3444,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3428,16 +3456,16 @@
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3445,10 +3473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3471,16 +3499,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3494,7 +3522,7 @@
         <v>78</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>78</v>
@@ -3530,7 +3558,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3542,16 +3570,16 @@
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3559,10 +3587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3585,13 +3613,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3642,7 +3670,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3654,16 +3682,16 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -3671,10 +3699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3697,16 +3725,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3756,7 +3784,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3768,16 +3796,16 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -3785,10 +3813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3811,70 +3839,70 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3889,24 +3917,24 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3929,19 +3957,19 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3966,19 +3994,19 @@
         <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -3988,7 +4016,7 @@
         <v>155</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4003,27 +4031,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>172</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4045,19 +4073,19 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4067,7 +4095,7 @@
         <v>78</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>78</v>
@@ -4082,11 +4110,11 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
@@ -4104,7 +4132,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4119,24 +4147,24 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>172</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4159,19 +4187,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4220,7 +4248,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4235,13 +4263,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4249,10 +4277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4275,19 +4303,19 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4336,7 +4364,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4354,7 +4382,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4365,10 +4393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4391,19 +4419,19 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4452,7 +4480,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4461,19 +4489,19 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4481,10 +4509,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4507,19 +4535,19 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4568,7 +4596,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4577,19 +4605,19 @@
         <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4597,10 +4625,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4623,19 +4651,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4684,7 +4712,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4699,10 +4727,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>172</v>
@@ -4713,10 +4741,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4739,19 +4767,19 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4800,7 +4828,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4812,13 +4840,13 @@
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -4829,10 +4857,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4855,13 +4883,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>169</v>
+        <v>326</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4941,10 +4969,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4973,7 +5001,7 @@
         <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>175</v>
+        <v>329</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>140</v>
@@ -5026,7 +5054,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5055,14 +5083,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5084,10 +5112,10 @@
         <v>137</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>140</v>
@@ -5142,7 +5170,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5171,10 +5199,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5197,17 +5225,17 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5232,13 +5260,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5256,7 +5284,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5274,7 +5302,7 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -5285,10 +5313,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5311,17 +5339,17 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5370,7 +5398,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5385,10 +5413,10 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -5399,10 +5427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5425,17 +5453,17 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5484,7 +5512,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5499,10 +5527,10 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5513,10 +5541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5539,17 +5567,17 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5598,7 +5626,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5613,10 +5641,10 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -5627,10 +5655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5653,17 +5681,17 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5712,7 +5740,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
